--- a/46643_Intercuenca_Medio_Bajo_Madre_de_Dios/_raw_reportes_xlsx/IDConfig_8067_completo.xlsx
+++ b/46643_Intercuenca_Medio_Bajo_Madre_de_Dios/_raw_reportes_xlsx/IDConfig_8067_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R30687c0e02c94b33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R0339b9a374cc4c80"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,171 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3953.6100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4708.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4571.9900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3905.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3506.9600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2565.2600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2152.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2216.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2415.7400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2750.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3319.5800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>12/08/2026</x:t>
         </x:is>
       </x:c>

--- a/46643_Intercuenca_Medio_Bajo_Madre_de_Dios/_raw_reportes_xlsx/IDConfig_8067_completo.xlsx
+++ b/46643_Intercuenca_Medio_Bajo_Madre_de_Dios/_raw_reportes_xlsx/IDConfig_8067_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R0339b9a374cc4c80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R22b03834912d4e59"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,696 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1631.3400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1796.2700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1613.1900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1860.0200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1883.9500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2122.0300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2250.8300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2222.1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1558.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1549.2800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1551.8400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1576.0100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1678.6300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1813.0600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2078.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1732.8700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1547.6800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1620.8700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1691.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1717.5100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1808.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1861.0900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1989.0600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2160.1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2105.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2337.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2150.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2092.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2415.2900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2389.0200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2317.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1969.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2043.3700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2182.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2441.2900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2944.3600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2526.3100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2376.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1926.3300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1886.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2002.6800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2131.0900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2318.7800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2587.3100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2944.9300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3356.8700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
